--- a/data/trans_camb/P3A_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,92</t>
+          <t>1,56; 4,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,24</t>
+          <t>1,02; 4,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,83</t>
+          <t>6,07; 10,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,64</t>
+          <t>2,37; 5,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,82</t>
+          <t>1,25; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 13,51</t>
+          <t>9,28; 13,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,79</t>
+          <t>2,42; 4,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,01</t>
+          <t>1,42; 4,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,67</t>
+          <t>8,54; 11,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,38; 311,42</t>
+          <t>52,43; 304,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,99; 257,42</t>
+          <t>31,22; 262,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184,45; 662,63</t>
+          <t>200,75; 686,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,81; 266,03</t>
+          <t>68,26; 273,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,75; 213,8</t>
+          <t>32,32; 225,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>274,05; 678,53</t>
+          <t>257,56; 611,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,65; 226,74</t>
+          <t>76,79; 220,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,17; 193,03</t>
+          <t>41,39; 190,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>280,87; 550,01</t>
+          <t>274,49; 557,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,5</t>
+          <t>-1,49; 0,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,29</t>
+          <t>-2,2; -0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,83</t>
+          <t>-1,44; 0,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,01</t>
+          <t>-0,95; 0,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,22</t>
+          <t>-1,39; 0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,22</t>
+          <t>-0,71; 1,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,48</t>
+          <t>-0,9; 0,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; -0,22</t>
+          <t>-1,47; -0,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,81</t>
+          <t>-0,68; 0,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,15; 26,99</t>
+          <t>-50,83; 26,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,56; -13,05</t>
+          <t>-71,93; -12,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,16; 44,02</t>
+          <t>-46,55; 47,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 79,41</t>
+          <t>-42,44; 68,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,49; 20,94</t>
+          <t>-62,95; 25,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 96,34</t>
+          <t>-29,29; 93,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 29,11</t>
+          <t>-36,89; 22,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,81; -11,84</t>
+          <t>-60,43; -14,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 49,22</t>
+          <t>-27,88; 44,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 0,02</t>
+          <t>-7,95; 0,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,23; -5,22</t>
+          <t>-12,29; -5,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -1,95</t>
+          <t>-9,55; -2,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,13</t>
+          <t>-4,59; 3,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -0,33</t>
+          <t>-7,1; -0,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 0,82</t>
+          <t>-5,34; 0,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 0,11</t>
+          <t>-5,61; 0,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -4,28</t>
+          <t>-8,82; -4,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -1,86</t>
+          <t>-6,45; -1,84</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 0,66</t>
+          <t>-54,25; 5,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-83,18; -46,62</t>
+          <t>-81,84; -47,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,5; -19,4</t>
+          <t>-61,95; -19,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 44,73</t>
+          <t>-44,21; 42,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,31; -4,51</t>
+          <t>-65,93; -7,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 14,79</t>
+          <t>-48,55; 9,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 1,94</t>
+          <t>-45,34; 3,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,22; -43,16</t>
+          <t>-71,8; -41,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,29; -19,08</t>
+          <t>-50,97; -18,59</t>
         </is>
       </c>
     </row>
@@ -1325,27 +1325,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,83</t>
+          <t>-1,18; 0,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; -0,66</t>
+          <t>-2,5; -0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,42</t>
+          <t>-0,87; 1,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,36</t>
+          <t>0,37; 2,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,79</t>
+          <t>-1,02; 0,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,29</t>
+          <t>-0,11; 1,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; -0,2</t>
+          <t>-1,45; -0,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,99</t>
+          <t>0,5; 1,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 23,82</t>
+          <t>-25,92; 24,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,5; -18,15</t>
+          <t>-54,05; -19,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 40,15</t>
+          <t>-19,22; 37,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,15; 87,49</t>
+          <t>9,87; 81,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 29,88</t>
+          <t>-28,76; 26,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,16; 116,41</t>
+          <t>30,51; 115,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 40,85</t>
+          <t>-3,38; 37,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,64; -5,24</t>
+          <t>-37,56; -7,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,92; 61,14</t>
+          <t>11,82; 59,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>11,09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>9,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,87</t>
+          <t>1,6; 4,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,35</t>
+          <t>0,83; 4,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,69</t>
+          <t>5,56; 10,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,78</t>
+          <t>2,26; 5,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,17</t>
+          <t>0,91; 4,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,37</t>
+          <t>9,13; 13,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,81</t>
+          <t>2,59; 5,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,07</t>
+          <t>1,48; 4,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 11,65</t>
+          <t>8,16; 11,26</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>366,68%</t>
+          <t>340,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>403,09%</t>
+          <t>396,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>394,2%</t>
+          <t>379,07%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,43; 304,46</t>
+          <t>52,66; 311,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,22; 262,56</t>
+          <t>27,69; 267,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>200,75; 686,62</t>
+          <t>180,46; 605,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68,26; 273,3</t>
+          <t>62,93; 264,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,32; 225,65</t>
+          <t>24,22; 201,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>257,56; 611,18</t>
+          <t>247,42; 611,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,79; 220,96</t>
+          <t>86,61; 243,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,39; 190,57</t>
+          <t>47,14; 190,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>274,49; 557,93</t>
+          <t>264,7; 529,3</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,44</t>
+          <t>-1,41; 0,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; -0,26</t>
+          <t>-2,01; -0,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,9</t>
+          <t>-0,94; 1,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,95</t>
+          <t>-0,84; 1,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,3</t>
+          <t>-1,52; 0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,17</t>
+          <t>-0,24; 1,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,38</t>
+          <t>-0,95; 0,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,29</t>
+          <t>-1,48; -0,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,79</t>
+          <t>-0,25; 1,1</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-6,95%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 26,45</t>
+          <t>-49,95; 35,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,93; -12,66</t>
+          <t>-70,56; -12,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,55; 47,61</t>
+          <t>-34,56; 64,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 68,42</t>
+          <t>-38,09; 76,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,95; 25,49</t>
+          <t>-64,57; 26,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 93,43</t>
+          <t>-9,98; 120,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 22,01</t>
+          <t>-38,3; 29,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,43; -14,67</t>
+          <t>-59,79; -11,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 44,18</t>
+          <t>-10,04; 67,79</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,61</t>
+          <t>-5,76</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,99</t>
+          <t>-4,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,35</t>
+          <t>-8,06; -0,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,29; -5,36</t>
+          <t>-12,48; -5,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; -2,23</t>
+          <t>-9,24; -2,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 3,02</t>
+          <t>-4,51; 3,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -0,67</t>
+          <t>-7,22; -0,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,57</t>
+          <t>-5,38; 0,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 0,17</t>
+          <t>-5,08; 0,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,82; -4,02</t>
+          <t>-9,03; -4,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; -1,84</t>
+          <t>-6,79; -1,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-43,93%</t>
+          <t>-45,13%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-36,65%</t>
+          <t>-37,36%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,25; 5,19</t>
+          <t>-53,97; 2,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,84; -47,95</t>
+          <t>-81,85; -48,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,95; -19,25</t>
+          <t>-61,59; -19,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,21; 42,98</t>
+          <t>-43,96; 45,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,93; -7,92</t>
+          <t>-69,17; -10,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 9,79</t>
+          <t>-48,73; 10,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,34; 3,49</t>
+          <t>-42,51; 6,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,8; -41,59</t>
+          <t>-72,31; -44,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,97; -18,59</t>
+          <t>-51,88; -17,82</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,83</t>
+          <t>-1,28; 0,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; -0,68</t>
+          <t>-2,52; -0,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,33</t>
+          <t>-0,57; 1,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,26</t>
+          <t>0,32; 2,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,72</t>
+          <t>-1,03; 0,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,15</t>
+          <t>1,8; 3,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,26</t>
+          <t>-0,08; 1,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; -0,25</t>
+          <t>-1,47; -0,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,99</t>
+          <t>1,0; 2,25</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 24,31</t>
+          <t>-28,01; 22,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,05; -19,05</t>
+          <t>-54,44; -19,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 37,92</t>
+          <t>-12,18; 42,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,87; 81,51</t>
+          <t>8,5; 80,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 26,41</t>
+          <t>-28,9; 29,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,51; 115,25</t>
+          <t>49,79; 131,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 37,74</t>
+          <t>-1,62; 40,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-37,56; -7,47</t>
+          <t>-37,5; -6,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11,82; 59,56</t>
+          <t>25,19; 68,82</t>
         </is>
       </c>
     </row>
